--- a/Project Outputs for Card_Reader/BOM/Bill of Materials-Card_Reader.xlsx
+++ b/Project Outputs for Card_Reader/BOM/Bill of Materials-Card_Reader.xlsx
@@ -1,43 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\Flash Card Reader Product\Card_Reader\Project Outputs for Card_Reader\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\Card_Reader\Project Outputs for Card_Reader\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCBD927-9AF7-4870-A7C8-95C7BE941404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC8F090D-11FF-40DB-BAE6-933B3126CB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{02C19135-2B5A-465A-AA38-4E0C3043509C}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{592BD668-68F3-4694-BE88-D26CCE97007C}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Card_Reader" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Bill of Materials-Card_Reader'!$1:$1</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="152">
   <si>
     <t>Comment</t>
   </si>
@@ -66,6 +54,21 @@
     <t>Manufacturer_Part_Number</t>
   </si>
   <si>
+    <t>SS14</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+  <si>
+    <t>BT1</t>
+  </si>
+  <si>
+    <t>DIOM5026X262N</t>
+  </si>
+  <si>
+    <t>HY Electronic</t>
+  </si>
+  <si>
     <t>10uF</t>
   </si>
   <si>
@@ -90,19 +93,16 @@
     <t>0.1uF</t>
   </si>
   <si>
-    <t>C2, C5, C16, C17, C18, C20, C21, C25</t>
-  </si>
-  <si>
-    <t>GRM033D70J224ME01D</t>
-  </si>
-  <si>
-    <t>GRM033Z71C104KE14J</t>
-  </si>
-  <si>
-    <t>C5755505</t>
-  </si>
-  <si>
-    <t>Murata Electronics</t>
+    <t>C2, C5, C16, C17, C18, C20, C21, C25, C27</t>
+  </si>
+  <si>
+    <t>CAPC1608X90N</t>
+  </si>
+  <si>
+    <t>0603B104K250CT</t>
+  </si>
+  <si>
+    <t>Kamaya</t>
   </si>
   <si>
     <t>1uF</t>
@@ -111,9 +111,6 @@
     <t>C3, C19, C22</t>
   </si>
   <si>
-    <t>CAPC1608X90N</t>
-  </si>
-  <si>
     <t>CL10A105KP8NNNC</t>
   </si>
   <si>
@@ -138,7 +135,7 @@
     <t>10nF</t>
   </si>
   <si>
-    <t>C7, C8, C9, C10, C11, C12, C13, C14</t>
+    <t>C7, C8, C9, C11, C12, C13, C14</t>
   </si>
   <si>
     <t>CAPC1005X55N</t>
@@ -198,19 +195,19 @@
     <t>Espressif Systems</t>
   </si>
   <si>
-    <t>AMS1117-3.3</t>
+    <t>AP7365-33EG-13</t>
+  </si>
+  <si>
+    <t>Power Supply</t>
   </si>
   <si>
     <t>IC2</t>
   </si>
   <si>
-    <t>SOT229P700X180-4N</t>
-  </si>
-  <si>
-    <t>C6186</t>
-  </si>
-  <si>
-    <t>UMW</t>
+    <t>SOT230P700X180-4N</t>
+  </si>
+  <si>
+    <t>Diodes Incorporated</t>
   </si>
   <si>
     <t>LM4890MM</t>
@@ -234,6 +231,9 @@
     <t>SOT95P270X145-6N</t>
   </si>
   <si>
+    <t>C2649360</t>
+  </si>
+  <si>
     <t>Microchip</t>
   </si>
   <si>
@@ -336,7 +336,7 @@
     <t>FS8205A</t>
   </si>
   <si>
-    <t>Transistor</t>
+    <t>MOSFET (N-Channel)</t>
   </si>
   <si>
     <t>Q1</t>
@@ -345,13 +345,31 @@
     <t>SOP65P640X120-8N</t>
   </si>
   <si>
+    <t>TECH PUBLIC</t>
+  </si>
+  <si>
+    <t>FDN340P</t>
+  </si>
+  <si>
+    <t>MOSFET (P-Channel)</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>SOT95P237X112-3N</t>
+  </si>
+  <si>
+    <t>onsemi</t>
+  </si>
+  <si>
     <t>10K</t>
   </si>
   <si>
     <t>Resistor</t>
   </si>
   <si>
-    <t>R1, R18, R19, R20, R21, R22, R25, R26, R30</t>
+    <t>R1, R19, R20, R21, R22, R25, R26, R30</t>
   </si>
   <si>
     <t>RESC1608X55N</t>
@@ -369,7 +387,7 @@
     <t>100R</t>
   </si>
   <si>
-    <t>R2, R3, R5, R7, R10, R11, R13, R15, R27</t>
+    <t>R2, R3, R5, R10, R11, R13, R15, R27</t>
   </si>
   <si>
     <t>RESC2013X65N</t>
@@ -387,7 +405,7 @@
     <t>220R</t>
   </si>
   <si>
-    <t>R4, R6, R8, R9, R12, R14, R16, R17</t>
+    <t>R4, R6, R8, R12, R14, R16, R17</t>
   </si>
   <si>
     <t>RC0603FR-07220RL</t>
@@ -408,7 +426,28 @@
     <t>1K</t>
   </si>
   <si>
-    <t>R28, R29, R31, R32</t>
+    <t>R28, R29, R31</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>R32</t>
+  </si>
+  <si>
+    <t>ERJ-3EKF2001V</t>
+  </si>
+  <si>
+    <t>Panasonic</t>
+  </si>
+  <si>
+    <t>CR0603-FX-1003GLF</t>
+  </si>
+  <si>
+    <t>R33</t>
+  </si>
+  <si>
+    <t>Bourns</t>
   </si>
   <si>
     <t>BOOT</t>
@@ -441,10 +480,7 @@
     <t>Undefined or Miscellaneous</t>
   </si>
   <si>
-    <t>U1, U2, U3, U4, U5, U6, U7, U8</t>
-  </si>
-  <si>
-    <t>onsemi</t>
+    <t>U1, U2, U3, U5, U6, U7, U8</t>
   </si>
 </sst>
 </file>
@@ -820,14 +856,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1399F4C-96CE-42B1-87FA-C0AFA0EF595D}">
-  <dimension ref="A1:I28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1CDBCE6-081F-4289-B78F-954D324A7C24}">
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="23.88671875" customWidth="1"/>
-    <col min="9" max="9" width="26.21875" customWidth="1"/>
+    <col min="7" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -873,326 +907,324 @@
         <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="1">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="1">
+        <v>6</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="1">
-        <v>8</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="1">
+        <v>9</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="1">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="1">
-        <v>8</v>
-      </c>
-      <c r="G6" s="1"/>
       <c r="H6" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F8" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1200,13 +1232,13 @@
         <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>71</v>
@@ -1215,8 +1247,12 @@
         <v>1</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="H14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
@@ -1238,19 +1274,15 @@
         <v>1</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>75</v>
-      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>81</v>
@@ -1259,85 +1291,85 @@
         <v>82</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>94</v>
@@ -1346,8 +1378,12 @@
         <v>1</v>
       </c>
       <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="H19" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
@@ -1369,12 +1405,8 @@
         <v>1</v>
       </c>
       <c r="G20" s="1"/>
-      <c r="H20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>98</v>
-      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
@@ -1390,77 +1422,73 @@
         <v>105</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F21" s="1">
-        <v>9</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="I21" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F22" s="1">
-        <v>9</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="I22" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="F23" s="1">
         <v>8</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1468,138 +1496,249 @@
         <v>119</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>120</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F24" s="1">
-        <v>2</v>
-      </c>
-      <c r="G24" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="H24" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="F25" s="1">
-        <v>4</v>
-      </c>
-      <c r="G25" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="H25" s="2" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F27" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="2" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F28" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F32" s="1">
+        <v>7</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>